--- a/artfynd/A 36195-2022 artfynd.xlsx
+++ b/artfynd/A 36195-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36195-2022 artfynd.xlsx
+++ b/artfynd/A 36195-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61196464</v>
+        <v>61196399</v>
       </c>
       <c r="B2" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>1439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Sammetstaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum martioflavum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>351164.4520115219</v>
+        <v>350994</v>
       </c>
       <c r="R2" t="n">
-        <v>6411704.162278949</v>
+        <v>6412015</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,24 +753,14 @@
           <t>2016-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-08-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I vägrenen samt i skogspartier längs med Hökhultvägen. Stort antal fruktkroppar. Arten återfinns även på ytterligare några ställen längs detta skogsklädda parti av Hökhultsvägen, på båda sidorna av vägen, framförallt norrut från den registrerade punkten.</t>
+          <t>Bestämning verifierad av Johan Nitare.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,6 +776,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Nedanför sandig ås, i vägskärning intill skogsväg.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,16 +801,11 @@
         <v>61196492</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -858,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>351110.9703739496</v>
+        <v>351111</v>
       </c>
       <c r="R3" t="n">
-        <v>6411788.774091938</v>
+        <v>6411789</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,19 +876,9 @@
           <t>2016-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -938,6 +913,237 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>60916225</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hökhultsvägen Hemsjö, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>350970</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6412033</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hemsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-08-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-08-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Västra sidan Hökhultsvägen, i vägrenen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Liljewall</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Liljewall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>61196464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hökhultsvägen Hemsjö, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>351164</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6411704</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hemsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-08-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I vägrenen samt i skogspartier längs med Hökhultvägen. Stort antal fruktkroppar. Arten återfinns även på ytterligare några ställen längs detta skogsklädda parti av Hökhultsvägen, på båda sidorna av vägen, framförallt norrut från den registrerade punkten.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Liljewall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Liljewall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36195-2022 artfynd.xlsx
+++ b/artfynd/A 36195-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61196399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61196492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60916225</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,8 +1164,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61196464</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>